--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_bus.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9380319009554191</v>
+        <v>0.938031900955419</v>
       </c>
       <c r="G2">
         <v>-1.130199521952451</v>
@@ -561,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.2917056037382958</v>
+        <v>0.2917056037382951</v>
       </c>
       <c r="G3">
-        <v>-29.17137735526041</v>
+        <v>-29.17137735526048</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -572,22 +572,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.282962610288493</v>
+        <v>4.282962610288495</v>
       </c>
       <c r="C4">
-        <v>148.3661769587498</v>
+        <v>148.3661769587499</v>
       </c>
       <c r="D4">
-        <v>0.627731916335411</v>
+        <v>0.6277319163354117</v>
       </c>
       <c r="E4">
-        <v>2.898438697960061</v>
+        <v>2.898438697960059</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051345</v>
+        <v>77.77984578051344</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -746,22 +746,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.070094227531965</v>
+        <v>1.070094227532346</v>
       </c>
       <c r="O2">
-        <v>0.9380319009575472</v>
+        <v>0.9380319009574459</v>
       </c>
       <c r="P2">
-        <v>1.053494350469103</v>
+        <v>1.053494350468705</v>
       </c>
       <c r="Q2">
-        <v>25.98965116738461</v>
+        <v>25.98965116739707</v>
       </c>
       <c r="R2">
-        <v>-91.13019952198886</v>
+        <v>-91.13019952201601</v>
       </c>
       <c r="S2">
-        <v>153.5693903185298</v>
+        <v>153.5693903185486</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.031611214669895</v>
+        <v>1.031611214669993</v>
       </c>
       <c r="O3">
-        <v>0.2917056037512294</v>
+        <v>0.2917056037512936</v>
       </c>
       <c r="P3">
-        <v>0.8906876332645006</v>
+        <v>0.8906876332644384</v>
       </c>
       <c r="Q3">
-        <v>7.091324389037671</v>
+        <v>7.091324389062517</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550767</v>
+        <v>-119.1713773550799</v>
       </c>
       <c r="S3">
-        <v>171.7794727726356</v>
+        <v>171.7794727726615</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -831,55 +831,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.709154423938284</v>
+        <v>3.709154423937071</v>
       </c>
       <c r="D4">
-        <v>3.709154423938284</v>
+        <v>3.709154423937071</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.8296261025332</v>
+        <v>42.82962610251919</v>
       </c>
       <c r="G4">
-        <v>42.8296261025332</v>
+        <v>42.82962610251919</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9526279648032107</v>
+        <v>0.9526279648032089</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648047162</v>
+        <v>0.9526279648047558</v>
       </c>
       <c r="Q4">
-        <v>-4.470463325006108E-11</v>
+        <v>-1.253993644999055E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999999844</v>
+        <v>-179.9999999999812</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279646110882</v>
+        <v>0.9526279646110866</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279649968384</v>
+        <v>0.9526279649968781</v>
       </c>
       <c r="Q5">
-        <v>1.116628898912448E-09</v>
+        <v>1.148794281838388E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999988231</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279646110882</v>
+        <v>0.9526279646110866</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279649968384</v>
+        <v>0.9526279649968781</v>
       </c>
       <c r="Q6">
-        <v>1.116628898912449E-09</v>
+        <v>1.148794281838288E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999988231</v>
+        <v>179.9999999988429</v>
       </c>
     </row>
   </sheetData>
@@ -1110,22 +1110,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.096878541938596</v>
+        <v>1.09687854193859</v>
       </c>
       <c r="O2">
-        <v>1.029837663667691</v>
+        <v>1.029837663667628</v>
       </c>
       <c r="P2">
-        <v>1.068709665745349</v>
+        <v>1.068709665745342</v>
       </c>
       <c r="Q2">
-        <v>27.98323699101714</v>
+        <v>27.98323699101546</v>
       </c>
       <c r="R2">
-        <v>-91.78162348160727</v>
+        <v>-91.78162348160745</v>
       </c>
       <c r="S2">
-        <v>151.211311285146</v>
+        <v>151.2113112851477</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1169,22 +1169,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.109634423210966</v>
+        <v>1.109634423210918</v>
       </c>
       <c r="O3">
-        <v>0.7617779018711788</v>
+        <v>0.761777901871072</v>
       </c>
       <c r="P3">
-        <v>0.9348070984869183</v>
+        <v>0.9348070984869522</v>
       </c>
       <c r="Q3">
-        <v>19.43181595267181</v>
+        <v>19.43181595267037</v>
       </c>
       <c r="R3">
-        <v>-104.2565908665072</v>
+        <v>-104.2565908665021</v>
       </c>
       <c r="S3">
-        <v>156.7400468039698</v>
+        <v>156.7400468039737</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1195,55 +1195,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.763086650675632</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="D4">
-        <v>1.763086650675632</v>
+        <v>1.763086650675506</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20.35837104744423</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="G4">
-        <v>20.35837104744423</v>
+        <v>20.35837104744278</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>1.075852895209894</v>
+        <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.6233452632552816</v>
+        <v>0.6233452632551814</v>
       </c>
       <c r="P4">
-        <v>0.9229411060010951</v>
+        <v>0.9229411060011539</v>
       </c>
       <c r="Q4">
-        <v>16.25665454943167</v>
+        <v>16.25665454943075</v>
       </c>
       <c r="R4">
-        <v>-104.9129785376941</v>
+        <v>-104.9129785376843</v>
       </c>
       <c r="S4">
-        <v>160.954389828646</v>
+        <v>160.9543898286496</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.075852895122511</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O5">
-        <v>0.6233452631756222</v>
+        <v>0.6233452631755221</v>
       </c>
       <c r="P5">
-        <v>0.9229411060760548</v>
+        <v>0.9229411060761135</v>
       </c>
       <c r="Q5">
-        <v>16.2566545497676</v>
+        <v>16.2566545497667</v>
       </c>
       <c r="R5">
-        <v>-104.912978523349</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S5">
-        <v>160.9543898314613</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.075852895122511</v>
+        <v>1.075852895122449</v>
       </c>
       <c r="O6">
-        <v>0.6233452631756222</v>
+        <v>0.6233452631755221</v>
       </c>
       <c r="P6">
-        <v>0.9229411060760548</v>
+        <v>0.9229411060761135</v>
       </c>
       <c r="Q6">
-        <v>16.2566545497676</v>
+        <v>16.2566545497667</v>
       </c>
       <c r="R6">
-        <v>-104.912978523349</v>
+        <v>-104.9129785233392</v>
       </c>
       <c r="S6">
-        <v>160.9543898314613</v>
+        <v>160.9543898314649</v>
       </c>
     </row>
   </sheetData>
@@ -1474,22 +1474,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.096878541938596</v>
+        <v>1.09687854193859</v>
       </c>
       <c r="O2">
-        <v>1.029837663667691</v>
+        <v>1.029837663667628</v>
       </c>
       <c r="P2">
-        <v>1.068709665745349</v>
+        <v>1.068709665745342</v>
       </c>
       <c r="Q2">
-        <v>27.98323699101714</v>
+        <v>27.98323699101546</v>
       </c>
       <c r="R2">
-        <v>-91.78162348160727</v>
+        <v>-91.78162348160745</v>
       </c>
       <c r="S2">
-        <v>151.211311285146</v>
+        <v>151.2113112851477</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1533,22 +1533,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.109634423210966</v>
+        <v>1.109634423210917</v>
       </c>
       <c r="O3">
-        <v>0.7617779018711788</v>
+        <v>0.7617779018710716</v>
       </c>
       <c r="P3">
-        <v>0.9348070984869183</v>
+        <v>0.9348070984869523</v>
       </c>
       <c r="Q3">
-        <v>19.43181595267181</v>
+        <v>19.43181595267036</v>
       </c>
       <c r="R3">
-        <v>-104.2565908665072</v>
+        <v>-104.2565908665021</v>
       </c>
       <c r="S3">
-        <v>156.7400468039698</v>
+        <v>156.7400468039737</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1559,55 +1559,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.763086650675632</v>
+        <v>1.763086650675505</v>
       </c>
       <c r="D4">
-        <v>1.763086650675632</v>
+        <v>1.763086650675505</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20.35837104744423</v>
+        <v>20.35837104744277</v>
       </c>
       <c r="G4">
-        <v>20.35837104744423</v>
+        <v>20.35837104744277</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>1.075852895209894</v>
+        <v>1.075852895209832</v>
       </c>
       <c r="O4">
-        <v>0.6233452632552816</v>
+        <v>0.6233452632551812</v>
       </c>
       <c r="P4">
-        <v>0.9229411060010951</v>
+        <v>0.9229411060011539</v>
       </c>
       <c r="Q4">
-        <v>16.25665454943167</v>
+        <v>16.25665454943074</v>
       </c>
       <c r="R4">
-        <v>-104.9129785376941</v>
+        <v>-104.9129785376843</v>
       </c>
       <c r="S4">
-        <v>160.954389828646</v>
+        <v>160.9543898286496</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.07585289511835</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O5">
-        <v>0.6233452631718289</v>
+        <v>0.6233452631717284</v>
       </c>
       <c r="P5">
-        <v>0.9229411060796244</v>
+        <v>0.9229411060796833</v>
       </c>
       <c r="Q5">
-        <v>16.2566545497836</v>
+        <v>16.25665454978268</v>
       </c>
       <c r="R5">
-        <v>-104.9129785226659</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S5">
-        <v>160.9543898315954</v>
+        <v>160.954389831599</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.07585289511835</v>
+        <v>1.075852895118288</v>
       </c>
       <c r="O6">
-        <v>0.6233452631718289</v>
+        <v>0.6233452631717283</v>
       </c>
       <c r="P6">
-        <v>0.9229411060796244</v>
+        <v>0.9229411060796832</v>
       </c>
       <c r="Q6">
-        <v>16.2566545497836</v>
+        <v>16.25665454978268</v>
       </c>
       <c r="R6">
-        <v>-104.9129785226659</v>
+        <v>-104.9129785226561</v>
       </c>
       <c r="S6">
-        <v>160.9543898315954</v>
+        <v>160.954389831599</v>
       </c>
     </row>
   </sheetData>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9821968591988028</v>
+        <v>0.9821968591989456</v>
       </c>
       <c r="O2">
-        <v>0.8500049525414368</v>
+        <v>0.850004952541402</v>
       </c>
       <c r="P2">
-        <v>0.9468598309457826</v>
+        <v>0.9468598309457217</v>
       </c>
       <c r="Q2">
-        <v>25.60992326808537</v>
+        <v>25.60992326808852</v>
       </c>
       <c r="R2">
-        <v>-92.65381631330838</v>
+        <v>-92.65381631331513</v>
       </c>
       <c r="S2">
-        <v>153.3606354236726</v>
+        <v>153.3606354236809</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1897,22 +1897,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401369729</v>
+        <v>0.9900703401370794</v>
       </c>
       <c r="O3">
-        <v>0.3617201835031932</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
-        <v>0.7649715466411645</v>
+        <v>0.7649715466411121</v>
       </c>
       <c r="Q3">
-        <v>8.150888684277191</v>
+        <v>8.150888684274459</v>
       </c>
       <c r="R3">
-        <v>-129.0915432241433</v>
+        <v>-129.0915432241893</v>
       </c>
       <c r="S3">
-        <v>169.4262793833429</v>
+        <v>169.4262793833645</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1923,55 +1923,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825514103</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="D4">
-        <v>3.119085825514103</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.01610081972227</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="G4">
-        <v>36.01610081972227</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8660254037879641</v>
+        <v>0.8660254037880056</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037882626</v>
+        <v>0.8660254037883346</v>
       </c>
       <c r="Q4">
-        <v>1.776666519128591E-10</v>
+        <v>1.72333333294283E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999997968</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660254036128463</v>
+        <v>0.8660254036128878</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8660254039633803</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q5">
-        <v>1.342072116256964E-09</v>
+        <v>1.336742883864954E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999986324</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8660254036128463</v>
+        <v>0.8660254036128878</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254039633803</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q6">
-        <v>1.342072116256963E-09</v>
+        <v>1.336742883864933E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999986324</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
   </sheetData>
@@ -2202,22 +2202,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9821968591988028</v>
+        <v>0.9821968591989456</v>
       </c>
       <c r="O2">
-        <v>0.8500049525414368</v>
+        <v>0.850004952541402</v>
       </c>
       <c r="P2">
-        <v>0.9468598309457826</v>
+        <v>0.9468598309457217</v>
       </c>
       <c r="Q2">
-        <v>25.60992326808537</v>
+        <v>25.60992326808852</v>
       </c>
       <c r="R2">
-        <v>-92.65381631330838</v>
+        <v>-92.65381631331513</v>
       </c>
       <c r="S2">
-        <v>153.3606354236726</v>
+        <v>153.3606354236809</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2261,22 +2261,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9900703401369729</v>
+        <v>0.9900703401370794</v>
       </c>
       <c r="O3">
-        <v>0.3617201835031932</v>
+        <v>0.3617201835030111</v>
       </c>
       <c r="P3">
-        <v>0.7649715466411645</v>
+        <v>0.7649715466411121</v>
       </c>
       <c r="Q3">
-        <v>8.150888684277191</v>
+        <v>8.150888684274459</v>
       </c>
       <c r="R3">
-        <v>-129.0915432241433</v>
+        <v>-129.0915432241893</v>
       </c>
       <c r="S3">
-        <v>169.4262793833429</v>
+        <v>169.4262793833645</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2287,55 +2287,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.119085825514103</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="D4">
-        <v>3.119085825514103</v>
+        <v>3.119085825515528</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36.01610081972227</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="G4">
-        <v>36.01610081972227</v>
+        <v>36.01610081973872</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8660254037879641</v>
+        <v>0.8660254037880056</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254037882626</v>
+        <v>0.8660254037883346</v>
       </c>
       <c r="Q4">
-        <v>1.776666519128591E-10</v>
+        <v>1.72333333294283E-10</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999997968</v>
+        <v>179.9999999998194</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660254036128463</v>
+        <v>0.8660254036128878</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8660254039633803</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q5">
-        <v>1.342072116256964E-09</v>
+        <v>1.336742883864954E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999986324</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8660254036128463</v>
+        <v>0.8660254036128878</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254039633803</v>
+        <v>0.8660254039634524</v>
       </c>
       <c r="Q6">
-        <v>1.342072116256963E-09</v>
+        <v>1.336742883864933E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999986324</v>
+        <v>179.9999999986551</v>
       </c>
     </row>
   </sheetData>
@@ -2566,22 +2566,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9991077190359311</v>
+        <v>0.9991077190359253</v>
       </c>
       <c r="O2">
-        <v>0.9333641900097112</v>
+        <v>0.9333641900095898</v>
       </c>
       <c r="P2">
-        <v>0.9681777323220995</v>
+        <v>0.9681777323222122</v>
       </c>
       <c r="Q2">
-        <v>27.82469744525146</v>
+        <v>27.82469744524451</v>
       </c>
       <c r="R2">
-        <v>-92.15705182751644</v>
+        <v>-92.15705182751169</v>
       </c>
       <c r="S2">
-        <v>151.2048467246506</v>
+        <v>151.2048467246548</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2625,22 +2625,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.018434506766472</v>
+        <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959568438</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
-        <v>0.8449321159940409</v>
+        <v>0.8449321159941328</v>
       </c>
       <c r="Q3">
-        <v>19.61176266475736</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
-        <v>-105.2709110729078</v>
+        <v>-105.2709110729077</v>
       </c>
       <c r="S3">
-        <v>156.1359474819708</v>
+        <v>156.1359474819764</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2651,55 +2651,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.518298439092253</v>
+        <v>1.518298439092604</v>
       </c>
       <c r="D4">
-        <v>1.518298439092253</v>
+        <v>1.518298439092604</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17.53180025040202</v>
+        <v>17.53180025040607</v>
       </c>
       <c r="G4">
-        <v>17.53180025040202</v>
+        <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119482</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.536799561077769</v>
+        <v>0.5367995610775461</v>
       </c>
       <c r="P4">
-        <v>0.852981284086228</v>
+        <v>0.8529812840863317</v>
       </c>
       <c r="Q4">
-        <v>15.93288697156595</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
-        <v>-101.723813849559</v>
+        <v>-101.7238138495564</v>
       </c>
       <c r="S4">
-        <v>162.0554462537812</v>
+        <v>162.0554462537874</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9573399674272666</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O5">
-        <v>0.5367995610221735</v>
+        <v>0.5367995610219506</v>
       </c>
       <c r="P5">
-        <v>0.8529812841637765</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q5">
-        <v>15.93288697234362</v>
+        <v>15.93288697233362</v>
       </c>
       <c r="R5">
-        <v>-101.7238138322597</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>162.0554462562273</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9573399674272666</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O6">
-        <v>0.5367995610221735</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>0.8529812841637765</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q6">
-        <v>15.93288697234362</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>-101.7238138322597</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>162.0554462562273</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -2930,22 +2930,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9991077190359311</v>
+        <v>0.9991077190359253</v>
       </c>
       <c r="O2">
-        <v>0.9333641900097112</v>
+        <v>0.9333641900095898</v>
       </c>
       <c r="P2">
-        <v>0.9681777323220995</v>
+        <v>0.9681777323222122</v>
       </c>
       <c r="Q2">
-        <v>27.82469744525146</v>
+        <v>27.82469744524451</v>
       </c>
       <c r="R2">
-        <v>-92.15705182751644</v>
+        <v>-92.15705182751169</v>
       </c>
       <c r="S2">
-        <v>151.2048467246506</v>
+        <v>151.2048467246548</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2989,22 +2989,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.018434506766472</v>
+        <v>1.018434506766488</v>
       </c>
       <c r="O3">
-        <v>0.7086876959568438</v>
+        <v>0.708687695956659</v>
       </c>
       <c r="P3">
-        <v>0.8449321159940409</v>
+        <v>0.8449321159941328</v>
       </c>
       <c r="Q3">
-        <v>19.61176266475736</v>
+        <v>19.61176266474868</v>
       </c>
       <c r="R3">
-        <v>-105.2709110729078</v>
+        <v>-105.2709110729077</v>
       </c>
       <c r="S3">
-        <v>156.1359474819708</v>
+        <v>156.1359474819764</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -3015,55 +3015,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.518298439092253</v>
+        <v>1.518298439092604</v>
       </c>
       <c r="D4">
-        <v>1.518298439092253</v>
+        <v>1.518298439092604</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17.53180025040202</v>
+        <v>17.53180025040607</v>
       </c>
       <c r="G4">
-        <v>17.53180025040202</v>
+        <v>17.53180025040607</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9573399675119482</v>
+        <v>0.9573399675119605</v>
       </c>
       <c r="O4">
-        <v>0.536799561077769</v>
+        <v>0.5367995610775461</v>
       </c>
       <c r="P4">
-        <v>0.852981284086228</v>
+        <v>0.8529812840863317</v>
       </c>
       <c r="Q4">
-        <v>15.93288697156595</v>
+        <v>15.93288697155595</v>
       </c>
       <c r="R4">
-        <v>-101.723813849559</v>
+        <v>-101.7238138495564</v>
       </c>
       <c r="S4">
-        <v>162.0554462537812</v>
+        <v>162.0554462537874</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9573399674272666</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O5">
-        <v>0.5367995610221735</v>
+        <v>0.5367995610219506</v>
       </c>
       <c r="P5">
-        <v>0.8529812841637765</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q5">
-        <v>15.93288697234362</v>
+        <v>15.93288697233362</v>
       </c>
       <c r="R5">
-        <v>-101.7238138322597</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S5">
-        <v>162.0554462562273</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9573399674272666</v>
+        <v>0.9573399674272789</v>
       </c>
       <c r="O6">
-        <v>0.5367995610221735</v>
+        <v>0.5367995610219505</v>
       </c>
       <c r="P6">
-        <v>0.8529812841637765</v>
+        <v>0.8529812841638801</v>
       </c>
       <c r="Q6">
-        <v>15.93288697234362</v>
+        <v>15.93288697233361</v>
       </c>
       <c r="R6">
-        <v>-101.7238138322597</v>
+        <v>-101.7238138322571</v>
       </c>
       <c r="S6">
-        <v>162.0554462562273</v>
+        <v>162.0554462562335</v>
       </c>
     </row>
   </sheetData>
@@ -3297,22 +3297,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.008855760173039</v>
+        <v>1.008855760167266</v>
       </c>
       <c r="O2">
-        <v>1.100000023846613</v>
+        <v>1.100000023846546</v>
       </c>
       <c r="P2">
-        <v>1.052974491498278</v>
+        <v>1.052974491486357</v>
       </c>
       <c r="Q2">
-        <v>30.27740992568527</v>
+        <v>30.27740992627456</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999943</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>145.8336491479605</v>
+        <v>145.8336491479224</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3359,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467347824912</v>
+        <v>0.6205467347487905</v>
       </c>
       <c r="O3">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.9549975894980027</v>
+        <v>0.9549975894427808</v>
       </c>
       <c r="Q3">
-        <v>30.02212423875053</v>
+        <v>30.02212424362662</v>
       </c>
       <c r="R3">
-        <v>-89.9999999999944</v>
+        <v>-89.99999999999648</v>
       </c>
       <c r="S3">
-        <v>124.2363584018584</v>
+        <v>124.2363584000751</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.14940305749119</v>
+        <v>4.149403057783843</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.9131794443759</v>
+        <v>47.91317944775516</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3403,43 +3403,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.5038029475428569</v>
+        <v>0.5038029475271065</v>
       </c>
       <c r="O4">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527589036403</v>
+        <v>0.8521527588318002</v>
       </c>
       <c r="Q4">
-        <v>41.72313522061911</v>
+        <v>41.72313522958809</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999416</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>116.1844690781363</v>
+        <v>116.1844690756951</v>
       </c>
       <c r="T4">
-        <v>4.149403057491191</v>
+        <v>4.149403057783843</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5038029476365905</v>
+        <v>0.5038029476208402</v>
       </c>
       <c r="O5">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P5">
-        <v>0.8521527587015898</v>
+        <v>0.8521527586297499</v>
       </c>
       <c r="Q5">
-        <v>41.72313524150528</v>
+        <v>41.72313525047427</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999416</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S5">
-        <v>116.1844690809003</v>
+        <v>116.1844690784591</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5038029476365905</v>
+        <v>0.5038029476208402</v>
       </c>
       <c r="O6">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P6">
-        <v>0.8521527587015898</v>
+        <v>0.8521527586297499</v>
       </c>
       <c r="Q6">
-        <v>41.72313524150528</v>
+        <v>41.72313525047427</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999416</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S6">
-        <v>116.1844690809003</v>
+        <v>116.1844690784591</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3679,22 +3679,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.008855760173039</v>
+        <v>1.008855760167266</v>
       </c>
       <c r="O2">
-        <v>1.100000023846613</v>
+        <v>1.100000023846546</v>
       </c>
       <c r="P2">
-        <v>1.052974491498278</v>
+        <v>1.052974491486357</v>
       </c>
       <c r="Q2">
-        <v>30.27740992568527</v>
+        <v>30.27740992627457</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999943</v>
+        <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>145.8336491479605</v>
+        <v>145.8336491479224</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6205467347824912</v>
+        <v>0.6205467347487905</v>
       </c>
       <c r="O3">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P3">
-        <v>0.9549975894980027</v>
+        <v>0.9549975894427802</v>
       </c>
       <c r="Q3">
-        <v>30.02212423875053</v>
+        <v>30.02212424362664</v>
       </c>
       <c r="R3">
-        <v>-89.9999999999944</v>
+        <v>-89.99999999999648</v>
       </c>
       <c r="S3">
-        <v>124.2363584018584</v>
+        <v>124.2363584000751</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.14940305749119</v>
+        <v>4.149403057783847</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>47.9131794443759</v>
+        <v>47.9131794477552</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -3785,43 +3785,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.5038029475428569</v>
+        <v>0.5038029475271065</v>
       </c>
       <c r="O4">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P4">
-        <v>0.8521527589036403</v>
+        <v>0.8521527588317999</v>
       </c>
       <c r="Q4">
-        <v>41.72313522061911</v>
+        <v>41.72313522958812</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999416</v>
+        <v>-89.99999999999623</v>
       </c>
       <c r="S4">
-        <v>116.1844690781363</v>
+        <v>116.184469075695</v>
       </c>
       <c r="T4">
-        <v>4.149403057491191</v>
+        <v>4.149403057783847</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5038029476410539</v>
+        <v>0.5038029476253036</v>
       </c>
       <c r="O5">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P5">
-        <v>0.8521527586919683</v>
+        <v>0.8521527586201284</v>
       </c>
       <c r="Q5">
-        <v>41.72313524249988</v>
+        <v>41.72313525146888</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999415</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S5">
-        <v>116.1844690810319</v>
+        <v>116.1844690785907</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5038029476410539</v>
+        <v>0.5038029476253036</v>
       </c>
       <c r="O6">
-        <v>1.100000023851119</v>
+        <v>1.100000023851052</v>
       </c>
       <c r="P6">
-        <v>0.8521527586919683</v>
+        <v>0.8521527586201285</v>
       </c>
       <c r="Q6">
-        <v>41.72313524249988</v>
+        <v>41.72313525146888</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999415</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S6">
-        <v>116.1844690810319</v>
+        <v>116.1844690785907</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4061,22 +4061,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.072419018453809</v>
+        <v>1.072419018453036</v>
       </c>
       <c r="O2">
-        <v>1.100000023843324</v>
+        <v>1.10000002384333</v>
       </c>
       <c r="P2">
-        <v>1.088827523082316</v>
+        <v>1.088827523081232</v>
       </c>
       <c r="Q2">
-        <v>29.85642581066776</v>
+        <v>29.85642581070923</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999427</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>148.6721122452182</v>
+        <v>148.6721122452009</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4123,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.956322218080594</v>
+        <v>0.9563222180761222</v>
       </c>
       <c r="O3">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P3">
-        <v>1.055630524136013</v>
+        <v>1.055630524130833</v>
       </c>
       <c r="Q3">
-        <v>28.69534087743089</v>
+        <v>28.69534087764962</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999434</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.6235429126757</v>
+        <v>142.6235429125326</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.259771139936445</v>
+        <v>1.259771139969438</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14.54658413519257</v>
+        <v>14.54658413557354</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4167,43 +4167,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9132295418427285</v>
+        <v>0.9132295418379797</v>
       </c>
       <c r="O4">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P4">
-        <v>1.016646408624119</v>
+        <v>1.016646408617081</v>
       </c>
       <c r="Q4">
-        <v>30.1933488059691</v>
+        <v>30.19334880632659</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999426</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S4">
-        <v>140.9330581980826</v>
+        <v>140.9330581979443</v>
       </c>
       <c r="T4">
-        <v>1.259771139936445</v>
+        <v>1.259771139969438</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.913229541850225</v>
+        <v>0.9132295418454761</v>
       </c>
       <c r="O5">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P5">
-        <v>1.016646408568652</v>
+        <v>1.016646408561614</v>
       </c>
       <c r="Q5">
-        <v>30.19334880986834</v>
+        <v>30.19334881022583</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999424</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S5">
-        <v>140.9330581997181</v>
+        <v>140.9330581995798</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.913229541850225</v>
+        <v>0.9132295418454761</v>
       </c>
       <c r="O6">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P6">
-        <v>1.016646408568652</v>
+        <v>1.016646408561614</v>
       </c>
       <c r="Q6">
-        <v>30.19334880986834</v>
+        <v>30.19334881022583</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999424</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S6">
-        <v>140.9330581997181</v>
+        <v>140.9330581995798</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.9380319009554193</v>
+        <v>0.9380319009554192</v>
       </c>
       <c r="G2">
-        <v>-1.130199521952445</v>
+        <v>-1.130199521952444</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.2917056037382966</v>
+        <v>0.291705603738296</v>
       </c>
       <c r="G3">
-        <v>-29.17137735526021</v>
+        <v>-29.17137735526025</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4414,22 +4414,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>4.282962610288489</v>
+        <v>4.282962610288493</v>
       </c>
       <c r="C4">
-        <v>148.3661769587497</v>
+        <v>148.3661769587498</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354118</v>
+        <v>0.6277319163354106</v>
       </c>
       <c r="E4">
-        <v>2.898438697960063</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>77.77984578051345</v>
+        <v>77.77984578051347</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4591,22 +4591,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.072419018453809</v>
+        <v>1.072419018453036</v>
       </c>
       <c r="O2">
-        <v>1.100000023843324</v>
+        <v>1.10000002384333</v>
       </c>
       <c r="P2">
-        <v>1.088827523082316</v>
+        <v>1.088827523081232</v>
       </c>
       <c r="Q2">
-        <v>29.85642581066776</v>
+        <v>29.85642581070923</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999427</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>148.6721122452182</v>
+        <v>148.6721122452009</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.956322218080594</v>
+        <v>0.9563222180761222</v>
       </c>
       <c r="O3">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P3">
-        <v>1.055630524136013</v>
+        <v>1.055630524130833</v>
       </c>
       <c r="Q3">
-        <v>28.69534087743089</v>
+        <v>28.69534087764962</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999434</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.6235429126757</v>
+        <v>142.6235429125326</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.259771139936445</v>
+        <v>1.259771139969438</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14.54658413519257</v>
+        <v>14.54658413557354</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4697,43 +4697,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9132295418427285</v>
+        <v>0.9132295418379797</v>
       </c>
       <c r="O4">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P4">
-        <v>1.016646408624119</v>
+        <v>1.016646408617081</v>
       </c>
       <c r="Q4">
-        <v>30.1933488059691</v>
+        <v>30.19334880632659</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999426</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S4">
-        <v>140.9330581980826</v>
+        <v>140.9330581979443</v>
       </c>
       <c r="T4">
-        <v>1.259771139936445</v>
+        <v>1.259771139969438</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9132295418505819</v>
+        <v>0.9132295418458332</v>
       </c>
       <c r="O5">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P5">
-        <v>1.01664640856601</v>
+        <v>1.016646408558973</v>
       </c>
       <c r="Q5">
-        <v>30.19334881005402</v>
+        <v>30.19334881041151</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999424</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S5">
-        <v>140.9330581997959</v>
+        <v>140.9330581996577</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9132295418505819</v>
+        <v>0.9132295418458332</v>
       </c>
       <c r="O6">
-        <v>1.100000023844962</v>
+        <v>1.100000023844968</v>
       </c>
       <c r="P6">
-        <v>1.01664640856601</v>
+        <v>1.016646408558973</v>
       </c>
       <c r="Q6">
-        <v>30.19334881005402</v>
+        <v>30.19334881041151</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999424</v>
+        <v>-89.99999999999633</v>
       </c>
       <c r="S6">
-        <v>140.9330581997959</v>
+        <v>140.9330581996577</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4973,22 +4973,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9315536824390599</v>
+        <v>0.9315536824327676</v>
       </c>
       <c r="O2">
-        <v>0.9999999999960595</v>
+        <v>0.9999999999960411</v>
       </c>
       <c r="P2">
-        <v>0.9826807015939983</v>
+        <v>0.9826807015885574</v>
       </c>
       <c r="Q2">
-        <v>28.96057504820126</v>
+        <v>28.96057504838301</v>
       </c>
       <c r="R2">
-        <v>-90.00000000000087</v>
+        <v>-89.99999999999639</v>
       </c>
       <c r="S2">
-        <v>146.0403260641652</v>
+        <v>146.0403260639204</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.680018778540221</v>
+        <v>0.6800187785078873</v>
       </c>
       <c r="O3">
-        <v>0.9999999999995008</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P3">
-        <v>0.980265672675772</v>
+        <v>0.9802656726571233</v>
       </c>
       <c r="Q3">
-        <v>21.63813480075657</v>
+        <v>21.63813480150454</v>
       </c>
       <c r="R3">
-        <v>-90.00000000000111</v>
+        <v>-89.99999999999662</v>
       </c>
       <c r="S3">
-        <v>130.1524719246516</v>
+        <v>130.1524719230285</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014554665436</v>
+        <v>2.826014554875526</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5070,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.6320052773978</v>
+        <v>32.63200527982371</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5079,43 +5079,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.547056749495356</v>
+        <v>0.5470567494623466</v>
       </c>
       <c r="O4">
-        <v>0.9999999999995006</v>
+        <v>0.9999999999994822</v>
       </c>
       <c r="P4">
-        <v>0.8611554266370592</v>
+        <v>0.8611554266059849</v>
       </c>
       <c r="Q4">
-        <v>30.64462611111757</v>
+        <v>30.64462611422798</v>
       </c>
       <c r="R4">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>123.13010856056</v>
+        <v>123.1301085584565</v>
       </c>
       <c r="T4">
-        <v>2.826014554665436</v>
+        <v>2.826014554875526</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5470567495152376</v>
+        <v>0.5470567494822284</v>
       </c>
       <c r="O5">
-        <v>0.9999999999995005</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P5">
-        <v>0.8611554264798513</v>
+        <v>0.8611554264487774</v>
       </c>
       <c r="Q5">
-        <v>30.64462612768854</v>
+        <v>30.64462613079896</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S5">
-        <v>123.1301085623381</v>
+        <v>123.1301085602346</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5470567495152376</v>
+        <v>0.5470567494822284</v>
       </c>
       <c r="O6">
-        <v>0.9999999999995005</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P6">
-        <v>0.8611554264798513</v>
+        <v>0.8611554264487774</v>
       </c>
       <c r="Q6">
-        <v>30.64462612768854</v>
+        <v>30.64462613079895</v>
       </c>
       <c r="R6">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S6">
-        <v>123.1301085623381</v>
+        <v>123.1301085602346</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5355,22 +5355,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9315536824390599</v>
+        <v>0.9315536824327676</v>
       </c>
       <c r="O2">
-        <v>0.9999999999960595</v>
+        <v>0.9999999999960411</v>
       </c>
       <c r="P2">
-        <v>0.9826807015939983</v>
+        <v>0.9826807015885574</v>
       </c>
       <c r="Q2">
-        <v>28.96057504820126</v>
+        <v>28.96057504838301</v>
       </c>
       <c r="R2">
-        <v>-90.00000000000087</v>
+        <v>-89.99999999999639</v>
       </c>
       <c r="S2">
-        <v>146.0403260641652</v>
+        <v>146.0403260639204</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.680018778540221</v>
+        <v>0.6800187785078873</v>
       </c>
       <c r="O3">
-        <v>0.9999999999995008</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P3">
-        <v>0.980265672675772</v>
+        <v>0.9802656726571233</v>
       </c>
       <c r="Q3">
-        <v>21.63813480075657</v>
+        <v>21.63813480150454</v>
       </c>
       <c r="R3">
-        <v>-90.00000000000111</v>
+        <v>-89.99999999999662</v>
       </c>
       <c r="S3">
-        <v>130.1524719246516</v>
+        <v>130.1524719230285</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2.826014554665436</v>
+        <v>2.826014554875526</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5452,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>32.6320052773978</v>
+        <v>32.63200527982371</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5461,43 +5461,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.547056749495356</v>
+        <v>0.5470567494623466</v>
       </c>
       <c r="O4">
-        <v>0.9999999999995006</v>
+        <v>0.9999999999994822</v>
       </c>
       <c r="P4">
-        <v>0.8611554266370592</v>
+        <v>0.8611554266059849</v>
       </c>
       <c r="Q4">
-        <v>30.64462611111757</v>
+        <v>30.64462611422798</v>
       </c>
       <c r="R4">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S4">
-        <v>123.13010856056</v>
+        <v>123.1301085584565</v>
       </c>
       <c r="T4">
-        <v>2.826014554665436</v>
+        <v>2.826014554875526</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5470567495152376</v>
+        <v>0.5470567494822284</v>
       </c>
       <c r="O5">
-        <v>0.9999999999995005</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P5">
-        <v>0.8611554264798513</v>
+        <v>0.8611554264487774</v>
       </c>
       <c r="Q5">
-        <v>30.64462612768854</v>
+        <v>30.64462613079896</v>
       </c>
       <c r="R5">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S5">
-        <v>123.1301085623381</v>
+        <v>123.1301085602346</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5470567495152376</v>
+        <v>0.5470567494822284</v>
       </c>
       <c r="O6">
-        <v>0.9999999999995005</v>
+        <v>0.9999999999994823</v>
       </c>
       <c r="P6">
-        <v>0.8611554264798513</v>
+        <v>0.8611554264487774</v>
       </c>
       <c r="Q6">
-        <v>30.64462612768854</v>
+        <v>30.64462613079895</v>
       </c>
       <c r="R6">
-        <v>-90.00000000000071</v>
+        <v>-89.99999999999622</v>
       </c>
       <c r="S6">
-        <v>123.1301085623381</v>
+        <v>123.1301085602346</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5737,22 +5737,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9745915261102379</v>
+        <v>0.9745915261094208</v>
       </c>
       <c r="O2">
-        <v>0.9999999999985772</v>
+        <v>0.9999999999986148</v>
       </c>
       <c r="P2">
-        <v>0.9918530105353008</v>
+        <v>0.9918530105344801</v>
       </c>
       <c r="Q2">
-        <v>29.71071470938245</v>
+        <v>29.71071470941317</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999716</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>148.5859961562333</v>
+        <v>148.5859961562051</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5799,22 +5799,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.878926597799126</v>
+        <v>0.8789265977951084</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
-        <v>0.9728049023675072</v>
+        <v>0.9728049023639357</v>
       </c>
       <c r="Q3">
-        <v>28.0332472355219</v>
+        <v>28.03324723565957</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999723</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.8915059391586</v>
+        <v>142.8915059389949</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.035710406388357</v>
+        <v>1.03571040641532</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11.95935363861629</v>
+        <v>11.95935363892763</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -5843,43 +5843,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8343784931079017</v>
+        <v>0.8343784931038759</v>
       </c>
       <c r="O4">
-        <v>0.9999999999998582</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367264165</v>
+        <v>0.9184277367208659</v>
       </c>
       <c r="Q4">
-        <v>30.72819116602499</v>
+        <v>30.72819116633073</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>141.3462823812374</v>
+        <v>141.3462823810989</v>
       </c>
       <c r="T4">
-        <v>1.035710406388357</v>
+        <v>1.03571040641532</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8343784931181799</v>
+        <v>0.8343784931141541</v>
       </c>
       <c r="O5">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P5">
-        <v>0.9184277366761899</v>
+        <v>0.9184277366706394</v>
       </c>
       <c r="Q5">
-        <v>30.72819116997557</v>
+        <v>30.72819117028131</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>141.3462823831014</v>
+        <v>141.3462823829629</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8343784931181799</v>
+        <v>0.8343784931141541</v>
       </c>
       <c r="O6">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P6">
-        <v>0.9184277366761899</v>
+        <v>0.9184277366706394</v>
       </c>
       <c r="Q6">
-        <v>30.72819116997557</v>
+        <v>30.72819117028131</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S6">
-        <v>141.3462823831014</v>
+        <v>141.3462823829629</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6119,22 +6119,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9745915261102379</v>
+        <v>0.9745915261094208</v>
       </c>
       <c r="O2">
-        <v>0.9999999999985772</v>
+        <v>0.9999999999986148</v>
       </c>
       <c r="P2">
-        <v>0.9918530105353008</v>
+        <v>0.9918530105344801</v>
       </c>
       <c r="Q2">
-        <v>29.71071470938245</v>
+        <v>29.71071470941317</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999716</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S2">
-        <v>148.5859961562333</v>
+        <v>148.5859961562051</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6181,22 +6181,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.878926597799126</v>
+        <v>0.8789265977951084</v>
       </c>
       <c r="O3">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P3">
-        <v>0.9728049023675072</v>
+        <v>0.9728049023639357</v>
       </c>
       <c r="Q3">
-        <v>28.0332472355219</v>
+        <v>28.03324723565957</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999723</v>
+        <v>-89.99999999999643</v>
       </c>
       <c r="S3">
-        <v>142.8915059391586</v>
+        <v>142.8915059389949</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.035710406388357</v>
+        <v>1.03571040641532</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6216,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11.95935363861629</v>
+        <v>11.95935363892763</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -6225,43 +6225,43 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.8343784931079017</v>
+        <v>0.8343784931038759</v>
       </c>
       <c r="O4">
-        <v>0.9999999999998582</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P4">
-        <v>0.9184277367264165</v>
+        <v>0.9184277367208659</v>
       </c>
       <c r="Q4">
-        <v>30.72819116602499</v>
+        <v>30.72819116633073</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S4">
-        <v>141.3462823812374</v>
+        <v>141.3462823810989</v>
       </c>
       <c r="T4">
-        <v>1.035710406388357</v>
+        <v>1.03571040641532</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8343784931181799</v>
+        <v>0.8343784931141541</v>
       </c>
       <c r="O5">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P5">
-        <v>0.9184277366761899</v>
+        <v>0.9184277366706394</v>
       </c>
       <c r="Q5">
-        <v>30.72819116997557</v>
+        <v>30.72819117028131</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S5">
-        <v>141.3462823831014</v>
+        <v>141.3462823829629</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8343784931181799</v>
+        <v>0.8343784931141541</v>
       </c>
       <c r="O6">
-        <v>0.9999999999998581</v>
+        <v>0.9999999999998956</v>
       </c>
       <c r="P6">
-        <v>0.9184277366761899</v>
+        <v>0.9184277366706394</v>
       </c>
       <c r="Q6">
-        <v>30.72819116997557</v>
+        <v>30.72819117028131</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999709</v>
+        <v>-89.99999999999631</v>
       </c>
       <c r="S6">
-        <v>141.3462823831014</v>
+        <v>141.3462823829629</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6501,22 +6501,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.032228710088265</v>
+        <v>1.032228710080033</v>
       </c>
       <c r="O2">
-        <v>0.9380319009590347</v>
+        <v>0.9380319009589637</v>
       </c>
       <c r="P2">
-        <v>1.040890135269432</v>
+        <v>1.040890135261071</v>
       </c>
       <c r="Q2">
-        <v>25.2995225934171</v>
+        <v>25.29952259362294</v>
       </c>
       <c r="R2">
-        <v>-91.1301995219563</v>
+        <v>-91.13019952198897</v>
       </c>
       <c r="S2">
-        <v>151.4964745430244</v>
+        <v>151.4964745427693</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6563,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8815655947465265</v>
+        <v>0.8815655946989951</v>
       </c>
       <c r="O3">
-        <v>0.2917056037516358</v>
+        <v>0.2917056037516226</v>
       </c>
       <c r="P3">
-        <v>0.7906583687516519</v>
+        <v>0.7906583687087714</v>
       </c>
       <c r="Q3">
-        <v>-1.718458459707053</v>
+        <v>-1.718458460145202</v>
       </c>
       <c r="R3">
-        <v>-119.1713773545602</v>
+        <v>-119.1713773545954</v>
       </c>
       <c r="S3">
-        <v>159.1708774444521</v>
+        <v>159.1708774428657</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6592,58 +6592,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.026925725499344</v>
+        <v>5.026925725599765</v>
       </c>
       <c r="D4">
-        <v>2.971978874787376</v>
+        <v>2.971978875003471</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593841626603</v>
+        <v>58.0459384174256</v>
       </c>
       <c r="G4">
-        <v>34.31745606768745</v>
+        <v>34.3174560701827</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.757517791846317</v>
+        <v>0.7575177917854184</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7575177918511363</v>
+        <v>0.7575177917902166</v>
       </c>
       <c r="Q4">
-        <v>-12.5250151709064</v>
+        <v>-12.52501517167082</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>167.4749848291187</v>
+        <v>167.4749848283541</v>
       </c>
       <c r="T4">
-        <v>3.629597112752477</v>
+        <v>3.629597113385642</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7575177916001882</v>
+        <v>0.7575177915392896</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7575177919710516</v>
+        <v>0.757517791910132</v>
       </c>
       <c r="Q5">
-        <v>-12.52501516768112</v>
+        <v>-12.52501516844552</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>167.4749848356385</v>
+        <v>167.4749848348739</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7575177916001882</v>
+        <v>0.7575177915392896</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7575177919710516</v>
+        <v>0.757517791910132</v>
       </c>
       <c r="Q6">
-        <v>-12.52501516768112</v>
+        <v>-12.52501516844552</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>167.4749848356385</v>
+        <v>167.4749848348739</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6883,22 +6883,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.032228710088265</v>
+        <v>1.032228710080033</v>
       </c>
       <c r="O2">
-        <v>0.9380319009590347</v>
+        <v>0.9380319009589637</v>
       </c>
       <c r="P2">
-        <v>1.040890135269432</v>
+        <v>1.040890135261071</v>
       </c>
       <c r="Q2">
-        <v>25.2995225934171</v>
+        <v>25.29952259362294</v>
       </c>
       <c r="R2">
-        <v>-91.1301995219563</v>
+        <v>-91.13019952198897</v>
       </c>
       <c r="S2">
-        <v>151.4964745430244</v>
+        <v>151.4964745427693</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6945,22 +6945,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8815655947465265</v>
+        <v>0.881565594698995</v>
       </c>
       <c r="O3">
-        <v>0.2917056037516358</v>
+        <v>0.2917056037516221</v>
       </c>
       <c r="P3">
-        <v>0.7906583687516519</v>
+        <v>0.7906583687087716</v>
       </c>
       <c r="Q3">
-        <v>-1.718458459707053</v>
+        <v>-1.71845846014524</v>
       </c>
       <c r="R3">
-        <v>-119.1713773545602</v>
+        <v>-119.1713773545954</v>
       </c>
       <c r="S3">
-        <v>159.1708774444521</v>
+        <v>159.1708774428657</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6974,58 +6974,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.026925725499344</v>
+        <v>5.026925725599762</v>
       </c>
       <c r="D4">
-        <v>2.971978874787376</v>
+        <v>2.971978875003471</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>58.04593841626603</v>
+        <v>58.04593841742555</v>
       </c>
       <c r="G4">
-        <v>34.31745606768745</v>
+        <v>34.3174560701827</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.757517791846317</v>
+        <v>0.7575177917854184</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.7575177918511363</v>
+        <v>0.7575177917902168</v>
       </c>
       <c r="Q4">
-        <v>-12.5250151709064</v>
+        <v>-12.52501517167087</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>167.4749848291187</v>
+        <v>167.4749848283541</v>
       </c>
       <c r="T4">
-        <v>3.629597112752477</v>
+        <v>3.629597113385639</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7575177915884677</v>
+        <v>0.7575177915275694</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7575177919767621</v>
+        <v>0.7575177919158427</v>
       </c>
       <c r="Q5">
-        <v>-12.52501516752754</v>
+        <v>-12.52501516829198</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>167.4749848359489</v>
+        <v>167.4749848351844</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7575177915884677</v>
+        <v>0.7575177915275694</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7575177919767621</v>
+        <v>0.7575177919158426</v>
       </c>
       <c r="Q6">
-        <v>-12.52501516752754</v>
+        <v>-12.52501516829198</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>167.4749848359489</v>
+        <v>167.4749848351844</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7265,22 +7265,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.087252142456469</v>
+        <v>1.087252142455643</v>
       </c>
       <c r="O2">
-        <v>1.0569664434903</v>
+        <v>1.056966443490334</v>
       </c>
       <c r="P2">
-        <v>1.074112601877916</v>
+        <v>1.074112601876989</v>
       </c>
       <c r="Q2">
-        <v>28.55316704499764</v>
+        <v>28.55316704502532</v>
       </c>
       <c r="R2">
-        <v>-91.34292556126823</v>
+        <v>-91.3429255612722</v>
       </c>
       <c r="S2">
-        <v>150.0036017617945</v>
+        <v>150.0036017617681</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049401079172844</v>
+        <v>1.04940107916796</v>
       </c>
       <c r="O3">
-        <v>0.8910570420399684</v>
+        <v>0.8910570420399742</v>
       </c>
       <c r="P3">
-        <v>0.9642317969900053</v>
+        <v>0.9642317969854517</v>
       </c>
       <c r="Q3">
-        <v>21.91294083456097</v>
+        <v>21.91294083466637</v>
       </c>
       <c r="R3">
-        <v>-99.1686792048723</v>
+        <v>-99.16867920487519</v>
       </c>
       <c r="S3">
-        <v>149.5927704017148</v>
+        <v>149.5927704015539</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7356,58 +7356,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.382520063886229</v>
+        <v>1.382520063880712</v>
       </c>
       <c r="D4">
-        <v>1.17670513866241</v>
+        <v>1.17670513870275</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.96396662089546</v>
+        <v>15.96396662083175</v>
       </c>
       <c r="G4">
-        <v>13.58742057127117</v>
+        <v>13.58742057173697</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>1.006459707645089</v>
+        <v>1.006459707639196</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380068</v>
+        <v>0.8020156209380072</v>
       </c>
       <c r="P4">
-        <v>0.9269140407918264</v>
+        <v>0.9269140407854378</v>
       </c>
       <c r="Q4">
-        <v>20.0541783582636</v>
+        <v>20.05417835845135</v>
       </c>
       <c r="R4">
-        <v>-99.52967390013853</v>
+        <v>-99.52967390014049</v>
       </c>
       <c r="S4">
-        <v>151.2507818978983</v>
+        <v>151.2507818977579</v>
       </c>
       <c r="T4">
-        <v>1.20256433132374</v>
+        <v>1.202564331389764</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.00645970758432</v>
+        <v>1.006459707578428</v>
       </c>
       <c r="O5">
-        <v>0.8020156208867607</v>
+        <v>0.8020156208867609</v>
       </c>
       <c r="P5">
-        <v>0.9269140408056241</v>
+        <v>0.9269140407992355</v>
       </c>
       <c r="Q5">
-        <v>20.05417836008782</v>
+        <v>20.05417836027556</v>
       </c>
       <c r="R5">
-        <v>-99.52967389296599</v>
+        <v>-99.52967389296796</v>
       </c>
       <c r="S5">
-        <v>151.2507819014106</v>
+        <v>151.2507819012702</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.00645970758432</v>
+        <v>1.006459707578428</v>
       </c>
       <c r="O6">
-        <v>0.8020156208867607</v>
+        <v>0.8020156208867609</v>
       </c>
       <c r="P6">
-        <v>0.9269140408056241</v>
+        <v>0.9269140407992355</v>
       </c>
       <c r="Q6">
-        <v>20.05417836008782</v>
+        <v>20.05417836027556</v>
       </c>
       <c r="R6">
-        <v>-99.52967389296599</v>
+        <v>-99.52967389296796</v>
       </c>
       <c r="S6">
-        <v>151.2507819014106</v>
+        <v>151.2507819012702</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7647,22 +7647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.087252142456469</v>
+        <v>1.087252142455643</v>
       </c>
       <c r="O2">
-        <v>1.0569664434903</v>
+        <v>1.056966443490333</v>
       </c>
       <c r="P2">
-        <v>1.074112601877916</v>
+        <v>1.074112601876989</v>
       </c>
       <c r="Q2">
-        <v>28.55316704499764</v>
+        <v>28.55316704502531</v>
       </c>
       <c r="R2">
-        <v>-91.34292556126823</v>
+        <v>-91.3429255612722</v>
       </c>
       <c r="S2">
-        <v>150.0036017617945</v>
+        <v>150.0036017617681</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7709,22 +7709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049401079172844</v>
+        <v>1.04940107916796</v>
       </c>
       <c r="O3">
-        <v>0.8910570420399684</v>
+        <v>0.8910570420399742</v>
       </c>
       <c r="P3">
-        <v>0.9642317969900053</v>
+        <v>0.9642317969854518</v>
       </c>
       <c r="Q3">
-        <v>21.91294083456097</v>
+        <v>21.91294083466637</v>
       </c>
       <c r="R3">
-        <v>-99.1686792048723</v>
+        <v>-99.16867920487518</v>
       </c>
       <c r="S3">
-        <v>149.5927704017148</v>
+        <v>149.5927704015539</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7738,58 +7738,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.382520063886229</v>
+        <v>1.382520063880712</v>
       </c>
       <c r="D4">
-        <v>1.17670513866241</v>
+        <v>1.176705138702749</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15.96396662089546</v>
+        <v>15.96396662083175</v>
       </c>
       <c r="G4">
-        <v>13.58742057127117</v>
+        <v>13.58742057173697</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642806</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934863</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162192</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.627731916363975</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>1.006459707645089</v>
+        <v>1.006459707639196</v>
       </c>
       <c r="O4">
-        <v>0.8020156209380068</v>
+        <v>0.802015620938007</v>
       </c>
       <c r="P4">
-        <v>0.9269140407918264</v>
+        <v>0.9269140407854378</v>
       </c>
       <c r="Q4">
-        <v>20.0541783582636</v>
+        <v>20.05417835845135</v>
       </c>
       <c r="R4">
-        <v>-99.52967390013853</v>
+        <v>-99.52967390014048</v>
       </c>
       <c r="S4">
-        <v>151.2507818978983</v>
+        <v>151.2507818977579</v>
       </c>
       <c r="T4">
-        <v>1.20256433132374</v>
+        <v>1.202564331389764</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.006459707581427</v>
+        <v>1.006459707575534</v>
       </c>
       <c r="O5">
         <v>0.8020156208843205</v>
       </c>
       <c r="P5">
-        <v>0.926914040806281</v>
+        <v>0.9269140407998927</v>
       </c>
       <c r="Q5">
-        <v>20.05417836017469</v>
+        <v>20.05417836036243</v>
       </c>
       <c r="R5">
-        <v>-99.52967389262443</v>
+        <v>-99.52967389262639</v>
       </c>
       <c r="S5">
-        <v>151.2507819015779</v>
+        <v>151.2507819014375</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.006459707581427</v>
+        <v>1.006459707575534</v>
       </c>
       <c r="O6">
         <v>0.8020156208843205</v>
       </c>
       <c r="P6">
-        <v>0.926914040806281</v>
+        <v>0.9269140407998926</v>
       </c>
       <c r="Q6">
-        <v>20.05417836017469</v>
+        <v>20.05417836036243</v>
       </c>
       <c r="R6">
-        <v>-99.52967389262443</v>
+        <v>-99.52967389262639</v>
       </c>
       <c r="S6">
-        <v>151.2507819015779</v>
+        <v>151.2507819014375</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8029,22 +8029,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9610470638633828</v>
+        <v>0.9610470638594746</v>
       </c>
       <c r="O2">
-        <v>0.8500049525398896</v>
+        <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649314737</v>
+        <v>0.9457332649301328</v>
       </c>
       <c r="Q2">
-        <v>24.7398195632198</v>
+        <v>24.73981956316841</v>
       </c>
       <c r="R2">
-        <v>-92.65381631334763</v>
+        <v>-92.65381631332207</v>
       </c>
       <c r="S2">
-        <v>151.8007058154448</v>
+        <v>151.8007058152363</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954916247</v>
+        <v>0.9239910954772123</v>
       </c>
       <c r="O3">
-        <v>0.3617201835036978</v>
+        <v>0.3617201835032898</v>
       </c>
       <c r="P3">
-        <v>0.7395562363552524</v>
+        <v>0.7395562363462336</v>
       </c>
       <c r="Q3">
-        <v>1.807833438302719</v>
+        <v>1.807833437614326</v>
       </c>
       <c r="R3">
-        <v>-129.0915432241966</v>
+        <v>-129.0915432241741</v>
       </c>
       <c r="S3">
-        <v>160.1110426267325</v>
+        <v>160.1110426255468</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8120,58 +8120,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256249437</v>
+        <v>3.921619256328453</v>
       </c>
       <c r="D4">
-        <v>2.491243992341185</v>
+        <v>2.491243992330687</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295866509664</v>
+        <v>45.28295866600905</v>
       </c>
       <c r="G4">
-        <v>28.76640779190443</v>
+        <v>28.76640779178321</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.7592484164502689</v>
+        <v>0.7592484164296976</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.759248416450563</v>
+        <v>0.7592484164304091</v>
       </c>
       <c r="Q4">
-        <v>-8.93008972720509</v>
+        <v>-8.930089728135304</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>171.0699102723324</v>
+        <v>171.0699102714301</v>
       </c>
       <c r="T4">
-        <v>2.06300821450409</v>
+        <v>2.063008214772792</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7592484162308477</v>
+        <v>0.7592484162102765</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7592484165825961</v>
+        <v>0.7592484165624421</v>
       </c>
       <c r="Q5">
-        <v>-8.930089725042615</v>
+        <v>-8.930089725972822</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>171.0699102759735</v>
+        <v>171.0699102750712</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7592484162308477</v>
+        <v>0.7592484162102765</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7592484165825961</v>
+        <v>0.7592484165624421</v>
       </c>
       <c r="Q6">
-        <v>-8.930089725042615</v>
+        <v>-8.930089725972827</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>171.0699102759735</v>
+        <v>171.0699102750712</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>1.056966443490338</v>
       </c>
       <c r="G2">
-        <v>-1.342925561278414</v>
+        <v>-1.342925561278412</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8910570420386134</v>
+        <v>0.8910570420386132</v>
       </c>
       <c r="G3">
-        <v>-9.168679204911147</v>
+        <v>-9.16867920491114</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8388,16 +8388,16 @@
         <v>45.36885473474869</v>
       </c>
       <c r="D4">
-        <v>0.627731916335411</v>
+        <v>0.6277319163354117</v>
       </c>
       <c r="E4">
-        <v>2.898438697960061</v>
+        <v>2.898438697960059</v>
       </c>
       <c r="F4">
-        <v>0.8020156209364413</v>
+        <v>0.802015620936441</v>
       </c>
       <c r="G4">
-        <v>45.00000000014394</v>
+        <v>45.00000000014396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8020156208851952</v>
+        <v>0.802015620885195</v>
       </c>
       <c r="G5">
-        <v>-9.529673893007812</v>
+        <v>-9.5296738930078</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8020156208851952</v>
+        <v>0.802015620885195</v>
       </c>
       <c r="G6">
-        <v>-9.529673893007812</v>
+        <v>-9.529673893007804</v>
       </c>
     </row>
   </sheetData>
@@ -8559,22 +8559,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9610470638633828</v>
+        <v>0.9610470638594746</v>
       </c>
       <c r="O2">
-        <v>0.8500049525398896</v>
+        <v>0.8500049525398535</v>
       </c>
       <c r="P2">
-        <v>0.9457332649314737</v>
+        <v>0.9457332649301328</v>
       </c>
       <c r="Q2">
-        <v>24.7398195632198</v>
+        <v>24.73981956316841</v>
       </c>
       <c r="R2">
-        <v>-92.65381631334763</v>
+        <v>-92.65381631332207</v>
       </c>
       <c r="S2">
-        <v>151.8007058154448</v>
+        <v>151.8007058152363</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9239910954916247</v>
+        <v>0.9239910954772123</v>
       </c>
       <c r="O3">
-        <v>0.3617201835036978</v>
+        <v>0.3617201835032898</v>
       </c>
       <c r="P3">
-        <v>0.7395562363552524</v>
+        <v>0.7395562363462336</v>
       </c>
       <c r="Q3">
-        <v>1.807833438302719</v>
+        <v>1.807833437614326</v>
       </c>
       <c r="R3">
-        <v>-129.0915432241966</v>
+        <v>-129.0915432241741</v>
       </c>
       <c r="S3">
-        <v>160.1110426267325</v>
+        <v>160.1110426255468</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8650,58 +8650,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.921619256249437</v>
+        <v>3.921619256328453</v>
       </c>
       <c r="D4">
-        <v>2.491243992341185</v>
+        <v>2.491243992330687</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>45.28295866509664</v>
+        <v>45.28295866600905</v>
       </c>
       <c r="G4">
-        <v>28.76640779190443</v>
+        <v>28.76640779178321</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.7592484164502689</v>
+        <v>0.7592484164296976</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.759248416450563</v>
+        <v>0.7592484164304091</v>
       </c>
       <c r="Q4">
-        <v>-8.93008972720509</v>
+        <v>-8.930089728135304</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>171.0699102723324</v>
+        <v>171.0699102714301</v>
       </c>
       <c r="T4">
-        <v>2.06300821450409</v>
+        <v>2.063008214772792</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7592484162308477</v>
+        <v>0.7592484162102765</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7592484165825961</v>
+        <v>0.7592484165624421</v>
       </c>
       <c r="Q5">
-        <v>-8.930089725042615</v>
+        <v>-8.930089725972822</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>171.0699102759735</v>
+        <v>171.0699102750712</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7592484162308477</v>
+        <v>0.7592484162102765</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7592484165825961</v>
+        <v>0.7592484165624421</v>
       </c>
       <c r="Q6">
-        <v>-8.930089725042615</v>
+        <v>-8.930089725972827</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>171.0699102759735</v>
+        <v>171.0699102750712</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8941,22 +8941,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9901411217609942</v>
+        <v>0.9901411217603693</v>
       </c>
       <c r="O2">
-        <v>0.9581045791304109</v>
+        <v>0.958104579130449</v>
       </c>
       <c r="P2">
-        <v>0.9758418560511378</v>
+        <v>0.9758418560505773</v>
       </c>
       <c r="Q2">
-        <v>28.35209815666929</v>
+        <v>28.35209815668079</v>
       </c>
       <c r="R2">
-        <v>-91.55789971897438</v>
+        <v>-91.5578997189799</v>
       </c>
       <c r="S2">
-        <v>150.0255731954904</v>
+        <v>150.0255731954607</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9003,22 +9003,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209966035</v>
+        <v>0.9677452209931274</v>
       </c>
       <c r="O3">
-        <v>0.8139299031202287</v>
+        <v>0.8139299031202699</v>
       </c>
       <c r="P3">
-        <v>0.8831724555091368</v>
+        <v>0.8831724555066111</v>
       </c>
       <c r="Q3">
-        <v>21.67250194551692</v>
+        <v>21.67250194553941</v>
       </c>
       <c r="R3">
-        <v>-99.65273561735978</v>
+        <v>-99.65273561736714</v>
       </c>
       <c r="S3">
-        <v>149.7426394549575</v>
+        <v>149.7426394547902</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9032,58 +9032,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.210751047572097</v>
+        <v>1.21075104757344</v>
       </c>
       <c r="D4">
-        <v>0.9664867209783102</v>
+        <v>0.9664867209998997</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>13.98054886474743</v>
+        <v>13.98054886476294</v>
       </c>
       <c r="G4">
-        <v>11.16002737050052</v>
+        <v>11.16002737074982</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9044874322255644</v>
+        <v>0.9044874322212385</v>
       </c>
       <c r="O4">
-        <v>0.7019303077933436</v>
+        <v>0.701930307793369</v>
       </c>
       <c r="P4">
-        <v>0.8518384757012379</v>
+        <v>0.8518384756969044</v>
       </c>
       <c r="Q4">
-        <v>19.80759473080412</v>
+        <v>19.80759473091594</v>
       </c>
       <c r="R4">
-        <v>-97.63434507041465</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
-        <v>152.8122609541106</v>
+        <v>152.8122609539748</v>
       </c>
       <c r="T4">
-        <v>0.9264880496230345</v>
+        <v>0.9264880496711532</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9044874321663953</v>
+        <v>0.9044874321620694</v>
       </c>
       <c r="O5">
-        <v>0.7019303077569948</v>
+        <v>0.7019303077570198</v>
       </c>
       <c r="P5">
-        <v>0.8518384757235944</v>
+        <v>0.8518384757192612</v>
       </c>
       <c r="Q5">
-        <v>19.80759473296762</v>
+        <v>19.80759473307945</v>
       </c>
       <c r="R5">
-        <v>-97.63434506176503</v>
+        <v>-97.63434506177373</v>
       </c>
       <c r="S5">
-        <v>152.8122609574563</v>
+        <v>152.8122609573205</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9044874321663953</v>
+        <v>0.9044874321620694</v>
       </c>
       <c r="O6">
-        <v>0.7019303077569948</v>
+        <v>0.7019303077570198</v>
       </c>
       <c r="P6">
-        <v>0.8518384757235944</v>
+        <v>0.8518384757192612</v>
       </c>
       <c r="Q6">
-        <v>19.80759473296762</v>
+        <v>19.80759473307944</v>
       </c>
       <c r="R6">
-        <v>-97.63434506176503</v>
+        <v>-97.63434506177373</v>
       </c>
       <c r="S6">
-        <v>152.8122609574563</v>
+        <v>152.8122609573205</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9323,22 +9323,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9901411217609942</v>
+        <v>0.9901411217603693</v>
       </c>
       <c r="O2">
-        <v>0.9581045791304109</v>
+        <v>0.958104579130449</v>
       </c>
       <c r="P2">
-        <v>0.9758418560511378</v>
+        <v>0.9758418560505773</v>
       </c>
       <c r="Q2">
-        <v>28.35209815666929</v>
+        <v>28.35209815668079</v>
       </c>
       <c r="R2">
-        <v>-91.55789971897438</v>
+        <v>-91.5578997189799</v>
       </c>
       <c r="S2">
-        <v>150.0255731954904</v>
+        <v>150.0255731954607</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9385,22 +9385,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9677452209966035</v>
+        <v>0.9677452209931274</v>
       </c>
       <c r="O3">
-        <v>0.8139299031202287</v>
+        <v>0.8139299031202699</v>
       </c>
       <c r="P3">
-        <v>0.8831724555091368</v>
+        <v>0.8831724555066111</v>
       </c>
       <c r="Q3">
-        <v>21.67250194551692</v>
+        <v>21.67250194553941</v>
       </c>
       <c r="R3">
-        <v>-99.65273561735978</v>
+        <v>-99.65273561736714</v>
       </c>
       <c r="S3">
-        <v>149.7426394549575</v>
+        <v>149.7426394547902</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9414,58 +9414,58 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1.210751047572097</v>
+        <v>1.21075104757344</v>
       </c>
       <c r="D4">
-        <v>0.9664867209783102</v>
+        <v>0.9664867209998997</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>13.98054886474743</v>
+        <v>13.98054886476294</v>
       </c>
       <c r="G4">
-        <v>11.16002737050052</v>
+        <v>11.16002737074982</v>
       </c>
       <c r="H4">
-        <v>7.100317911562573</v>
+        <v>7.100317910361327</v>
       </c>
       <c r="I4">
-        <v>1.94006366450855</v>
+        <v>1.940063664511512</v>
       </c>
       <c r="J4">
-        <v>1.11375188025369</v>
+        <v>1.11375188025397</v>
       </c>
       <c r="K4">
-        <v>3.006397543749494</v>
+        <v>3.006397543748691</v>
       </c>
       <c r="L4">
-        <v>1.113751880234299</v>
+        <v>1.113751880233242</v>
       </c>
       <c r="M4">
-        <v>3.006397543746158</v>
+        <v>3.006397543745534</v>
       </c>
       <c r="N4">
-        <v>0.9044874322255644</v>
+        <v>0.9044874322212385</v>
       </c>
       <c r="O4">
-        <v>0.7019303077933436</v>
+        <v>0.701930307793369</v>
       </c>
       <c r="P4">
-        <v>0.8518384757012379</v>
+        <v>0.8518384756969044</v>
       </c>
       <c r="Q4">
-        <v>19.80759473080412</v>
+        <v>19.80759473091594</v>
       </c>
       <c r="R4">
-        <v>-97.63434507041465</v>
+        <v>-97.63434507042335</v>
       </c>
       <c r="S4">
-        <v>152.8122609541106</v>
+        <v>152.8122609539748</v>
       </c>
       <c r="T4">
-        <v>0.9264880496230345</v>
+        <v>0.9264880496711532</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9044874321663953</v>
+        <v>0.9044874321620694</v>
       </c>
       <c r="O5">
-        <v>0.7019303077569948</v>
+        <v>0.7019303077570198</v>
       </c>
       <c r="P5">
-        <v>0.8518384757235944</v>
+        <v>0.8518384757192612</v>
       </c>
       <c r="Q5">
-        <v>19.80759473296762</v>
+        <v>19.80759473307945</v>
       </c>
       <c r="R5">
-        <v>-97.63434506176503</v>
+        <v>-97.63434506177373</v>
       </c>
       <c r="S5">
-        <v>152.8122609574563</v>
+        <v>152.8122609573205</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9044874321663953</v>
+        <v>0.9044874321620694</v>
       </c>
       <c r="O6">
-        <v>0.7019303077569948</v>
+        <v>0.7019303077570198</v>
       </c>
       <c r="P6">
-        <v>0.8518384757235944</v>
+        <v>0.8518384757192612</v>
       </c>
       <c r="Q6">
-        <v>19.80759473296762</v>
+        <v>19.80759473307944</v>
       </c>
       <c r="R6">
-        <v>-97.63434506176503</v>
+        <v>-97.63434506177373</v>
       </c>
       <c r="S6">
-        <v>152.8122609574563</v>
+        <v>152.8122609573205</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8910570420386137</v>
+        <v>0.8910570420386135</v>
       </c>
       <c r="G3">
-        <v>-9.16867920491114</v>
+        <v>-9.168679204911136</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9676,22 +9676,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>1.309686024696609</v>
+        <v>1.30968602469661</v>
       </c>
       <c r="C4">
-        <v>45.36885473474868</v>
+        <v>45.36885473474869</v>
       </c>
       <c r="D4">
-        <v>0.6277319163354118</v>
+        <v>0.6277319163354106</v>
       </c>
       <c r="E4">
-        <v>2.898438697960063</v>
+        <v>2.898438697960061</v>
       </c>
       <c r="F4">
         <v>0.8020156209364414</v>
       </c>
       <c r="G4">
-        <v>45.00000000014397</v>
+        <v>45.00000000014396</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.802015620882755</v>
+        <v>0.8020156208827551</v>
       </c>
       <c r="G6">
-        <v>-9.529673892666253</v>
+        <v>-9.529673892666251</v>
       </c>
     </row>
   </sheetData>
@@ -9793,7 +9793,7 @@
         <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408782</v>
+        <v>-2.653816313408785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9813,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3617201835011319</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526811</v>
+        <v>-39.09154322526815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9824,22 +9824,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.601610081969432</v>
+        <v>3.601610081969431</v>
       </c>
       <c r="C4">
-        <v>124.7634330204673</v>
+        <v>124.7634330204672</v>
       </c>
       <c r="D4">
         <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.6723164331698</v>
+        <v>69.67231643316981</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9941,7 +9941,7 @@
         <v>0.8500049525313291</v>
       </c>
       <c r="G2">
-        <v>-2.653816313408782</v>
+        <v>-2.653816313408785</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9961,10 +9961,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3617201835011319</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="G3">
-        <v>-39.09154322526811</v>
+        <v>-39.09154322526815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9972,22 +9972,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>3.601610081969432</v>
+        <v>3.601610081969431</v>
       </c>
       <c r="C4">
-        <v>124.7634330204673</v>
+        <v>124.7634330204672</v>
       </c>
       <c r="D4">
         <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>69.6723164331698</v>
+        <v>69.67231643316981</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10089,7 +10089,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992042</v>
+        <v>-1.557899718992045</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8139299031165275</v>
+        <v>0.8139299031165274</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430418</v>
+        <v>-9.652735617430428</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10129,13 +10129,13 @@
         <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986815</v>
+        <v>44.99999999986814</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532579</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G5">
-        <v>-7.634345061849613</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532579</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G6">
-        <v>-7.634345061849613</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
   </sheetData>
@@ -10237,7 +10237,7 @@
         <v>0.9581045791269168</v>
       </c>
       <c r="G2">
-        <v>-1.557899718992042</v>
+        <v>-1.557899718992045</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.8139299031165275</v>
+        <v>0.8139299031165274</v>
       </c>
       <c r="G3">
-        <v>-9.652735617430418</v>
+        <v>-9.652735617430428</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10277,13 +10277,13 @@
         <v>1.113751880252859</v>
       </c>
       <c r="E4">
-        <v>3.00639754374561</v>
+        <v>3.006397543745611</v>
       </c>
       <c r="F4">
         <v>0.7019303077896069</v>
       </c>
       <c r="G4">
-        <v>44.99999999986815</v>
+        <v>44.99999999986814</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7019303077532579</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G5">
-        <v>-7.634345061849613</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.7019303077532579</v>
+        <v>0.7019303077532578</v>
       </c>
       <c r="G6">
-        <v>-7.634345061849613</v>
+        <v>-7.634345061849633</v>
       </c>
     </row>
   </sheetData>
@@ -10442,22 +10442,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.070094227531965</v>
+        <v>1.070094227532346</v>
       </c>
       <c r="O2">
-        <v>0.9380319009575472</v>
+        <v>0.9380319009574459</v>
       </c>
       <c r="P2">
-        <v>1.053494350469103</v>
+        <v>1.053494350468705</v>
       </c>
       <c r="Q2">
-        <v>25.98965116738461</v>
+        <v>25.98965116739708</v>
       </c>
       <c r="R2">
-        <v>-91.13019952198886</v>
+        <v>-91.130199522016</v>
       </c>
       <c r="S2">
-        <v>153.5693903185298</v>
+        <v>153.5693903185486</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -10501,22 +10501,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.031611214669895</v>
+        <v>1.031611214669993</v>
       </c>
       <c r="O3">
-        <v>0.2917056037512294</v>
+        <v>0.2917056037512942</v>
       </c>
       <c r="P3">
-        <v>0.8906876332645006</v>
+        <v>0.8906876332644384</v>
       </c>
       <c r="Q3">
-        <v>7.091324389037671</v>
+        <v>7.091324389062546</v>
       </c>
       <c r="R3">
-        <v>-119.1713773550767</v>
+        <v>-119.1713773550798</v>
       </c>
       <c r="S3">
-        <v>171.7794727726356</v>
+        <v>171.7794727726615</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -10527,55 +10527,55 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>3.709154423938284</v>
+        <v>3.70915442393707</v>
       </c>
       <c r="D4">
-        <v>3.709154423938284</v>
+        <v>3.70915442393707</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>42.8296261025332</v>
+        <v>42.82962610251918</v>
       </c>
       <c r="G4">
-        <v>42.8296261025332</v>
+        <v>42.82962610251918</v>
       </c>
       <c r="H4">
-        <v>3.69806933584404</v>
+        <v>3.698069334642805</v>
       </c>
       <c r="I4">
-        <v>1.935851082932446</v>
+        <v>1.935851082934864</v>
       </c>
       <c r="J4">
-        <v>0.6277319163167385</v>
+        <v>0.6277319163162196</v>
       </c>
       <c r="K4">
-        <v>2.898438697979347</v>
+        <v>2.898438697979807</v>
       </c>
       <c r="L4">
-        <v>0.6277319163646856</v>
+        <v>0.6277319163639755</v>
       </c>
       <c r="M4">
-        <v>2.898438697959121</v>
+        <v>2.898438697959989</v>
       </c>
       <c r="N4">
-        <v>0.9526279648032107</v>
+        <v>0.952627964803209</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279648047162</v>
+        <v>0.9526279648047559</v>
       </c>
       <c r="Q4">
-        <v>-4.470463325006108E-11</v>
+        <v>-1.250596096833237E-11</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999999844</v>
+        <v>-179.9999999999812</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9526279646198211</v>
+        <v>0.9526279646198196</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.9526279649881056</v>
+        <v>0.9526279649881453</v>
       </c>
       <c r="Q5">
-        <v>1.063839402754912E-09</v>
+        <v>1.096058037250823E-09</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
       <c r="S5">
-        <v>179.9999999988758</v>
+        <v>179.9999999988956</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9526279646198211</v>
+        <v>0.9526279646198196</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279649881056</v>
+        <v>0.9526279649881454</v>
       </c>
       <c r="Q6">
-        <v>1.063839402754912E-09</v>
+        <v>1.096058037250845E-09</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999988758</v>
+        <v>179.9999999988956</v>
       </c>
     </row>
   </sheetData>
